--- a/i_test/test_D3_coorte_con_caratterizzazione/spf2025.xlsx
+++ b/i_test/test_D3_coorte_con_caratterizzazione/spf2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="24">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -34,6 +34,9 @@
     <t xml:space="preserve">P01</t>
   </si>
   <si>
+    <t xml:space="preserve">aaaaaxx</t>
+  </si>
+  <si>
     <t xml:space="preserve">aaaabxx</t>
   </si>
   <si>
@@ -46,13 +49,34 @@
     <t xml:space="preserve">aaaaexx</t>
   </si>
   <si>
-    <t xml:space="preserve">aaaaaxx</t>
+    <t xml:space="preserve">bbbbxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baaabxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baaacxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baaadyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baaaexx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caaaexx</t>
   </si>
   <si>
     <t xml:space="preserve">aaaaeyy</t>
   </si>
   <si>
     <t xml:space="preserve">P02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baaaaxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baaaeyy</t>
   </si>
   <si>
     <t xml:space="preserve">P03</t>
@@ -192,7 +216,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>20251002</v>
+        <v>20250901</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -203,7 +227,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>20251003</v>
+        <v>20250902</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -214,7 +238,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>20251004</v>
+        <v>20250903</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
@@ -225,7 +249,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>20251005</v>
+        <v>20250904</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
@@ -236,7 +260,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>20251101</v>
+        <v>20250905</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -247,10 +271,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>20251102</v>
+        <v>20250901</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -258,10 +282,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>20251103</v>
+        <v>20250902</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -269,10 +293,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>20251104</v>
+        <v>20250903</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -280,148 +304,128 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>20251105</v>
+        <v>20250904</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>20251001</v>
+        <v>20250905</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+        <v>13</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>20251002</v>
+        <v>20251001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>20251002</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>20251003</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>20251004</v>
+        <v>20251003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+        <v>11</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>20251005</v>
+        <v>20251004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>20251101</v>
+        <v>20251005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+        <v>13</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>20251102</v>
+        <v>20251002</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>20251103</v>
+        <v>20251002</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>20251104</v>
+        <v>20251003</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>20251105</v>
+        <v>20251004</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>20251201</v>
+        <v>20251005</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>8</v>
@@ -429,32 +433,32 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>20251002</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>20251202</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>20251203</v>
+        <v>20251002</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>20251204</v>
+        <v>20251003</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6</v>
@@ -462,307 +466,307 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>20251001</v>
+        <v>20251004</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>20251002</v>
+        <v>20251005</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>20251003</v>
+        <v>20251005</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>20251004</v>
+        <v>20251101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>20251005</v>
+        <v>20251102</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>20251101</v>
+        <v>20251103</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>20251102</v>
+        <v>20251104</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>20251103</v>
+        <v>20251105</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>20251104</v>
+        <v>20251101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>20251105</v>
+        <v>20251102</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>20251103</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>20251201</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>20251202</v>
+        <v>20251104</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>20251203</v>
+        <v>20251105</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>20251204</v>
+        <v>20251101</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>20251204</v>
+        <v>20251102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>20251001</v>
+        <v>20251103</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>20251002</v>
+        <v>20251104</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>20251003</v>
+        <v>20251105</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>20251004</v>
+        <v>20251201</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>20251005</v>
+        <v>20251202</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>20251101</v>
+        <v>20251203</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>20251102</v>
+        <v>20251204</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>20251103</v>
+        <v>20251204</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>20251104</v>
+        <v>20251001</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>20251105</v>
+        <v>20251002</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>20251104</v>
+        <v>20251003</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>20251105</v>
+        <v>20251004</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>20251201</v>
+        <v>20251005</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>8</v>
@@ -770,175 +774,195 @@
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>20251202</v>
+        <v>20251101</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>20251203</v>
+        <v>20251102</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>20251204</v>
+        <v>20251103</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>20251204</v>
+        <v>20251104</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>20251206</v>
+        <v>20251105</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>20250901</v>
+        <v>20251201</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>20250902</v>
+        <v>20251202</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>20250903</v>
+        <v>20251203</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>20250904</v>
+        <v>20251204</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>20250905</v>
+        <v>20251204</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>20251002</v>
+        <v>20251201</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>20251003</v>
+        <v>20251202</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>20251004</v>
+        <v>20251203</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>20251005</v>
+        <v>20251204</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>20251101</v>
+        <v>20251204</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>20251102</v>
+        <v>20251001</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>4</v>
@@ -946,10 +970,10 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>20251103</v>
+        <v>20251002</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>5</v>
@@ -957,10 +981,10 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>20251104</v>
+        <v>20251003</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -968,21 +992,21 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>20251105</v>
+        <v>20251004</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>20251201</v>
+        <v>20251005</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>8</v>
@@ -990,10 +1014,10 @@
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>20251202</v>
+        <v>20251101</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>4</v>
@@ -1001,10 +1025,10 @@
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>20251203</v>
+        <v>20251102</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>5</v>
@@ -1012,10 +1036,10 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>20251204</v>
+        <v>20251103</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>6</v>
@@ -1023,32 +1047,32 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>20251204</v>
+        <v>20251104</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>20251105</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>20251201</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>20251202</v>
+        <v>20251201</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>4</v>
@@ -1056,10 +1080,10 @@
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>20251203</v>
+        <v>20251202</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -1067,10 +1091,10 @@
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>20251204</v>
+        <v>20251203</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -1078,70 +1102,343 @@
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B81" s="1" t="n">
         <v>20251204</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1"/>
+      <c r="A82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>20251001</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1"/>
+      <c r="A84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>20251002</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1"/>
+      <c r="A85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>20251003</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1"/>
+      <c r="A86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>20251004</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1"/>
+      <c r="A87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>20251005</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1"/>
+      <c r="A88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>20251101</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1"/>
+      <c r="A89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>20251102</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1"/>
+      <c r="A90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>20251103</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1"/>
+      <c r="A91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>20251104</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1"/>
+      <c r="A92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>20251105</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1"/>
+      <c r="A93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>20251104</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1"/>
+      <c r="A94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>20251105</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1"/>
+      <c r="A95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>20251201</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>20251202</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>20251203</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>20251206</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>20251201</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>20251202</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>20251203</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
